--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104532_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104532_W9.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1215</v>
+        <v>6.3527</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8402</v>
+        <v>5.8857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2813</v>
+        <v>0.4669</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9491</v>
+        <v>3.9533</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9437</v>
+        <v>3.9379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0054</v>
+        <v>0.0153</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7194</v>
+        <v>3.704</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0477</v>
+        <v>3.0337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2297</v>
+        <v>0.2493</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8959</v>
+        <v>0.9043</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3493</v>
+        <v>-0.1242</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1603</v>
+        <v>0.232</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9289</v>
+        <v>5.1962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8777</v>
+        <v>1.3332</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0512</v>
+        <v>3.863</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8728</v>
+        <v>2.8835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6924</v>
+        <v>0.7058</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1804</v>
+        <v>2.1777</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3895</v>
+        <v>2.3789</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L3" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4833</v>
+        <v>0.5046</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2368</v>
+        <v>0.0152</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3015</v>
+        <v>0.0805</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.465</v>
+        <v>2.2618</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9053</v>
+        <v>1.1738</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4402</v>
+        <v>1.088</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2218</v>
+        <v>1.9465</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1284</v>
+        <v>2.2636</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.3172</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5248</v>
+        <v>1.9141</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4129</v>
+        <v>2.2645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>-0.3505</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.303</v>
+        <v>0.0324</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2844</v>
+        <v>-0.0009</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0186</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7381</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8075</v>
+        <v>-0.0283</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9306</v>
+        <v>0.1143</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4949</v>
+        <v>1.3675</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2946</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3908</v>
+        <v>1.9097</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1524</v>
+        <v>3.5564</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2384</v>
+        <v>-1.6467</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9515</v>
+        <v>2.7553</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2713</v>
+        <v>2.8208</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3198</v>
+        <v>-0.0655</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9477</v>
+        <v>3.5823</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2889</v>
+        <v>2.7784</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3413</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0038</v>
+        <v>-0.827</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0176</v>
+        <v>0.0424</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0214</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2044</v>
+        <v>-0.0324</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0998</v>
+        <v>-0.0258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3042</v>
+        <v>-0.0066</v>
       </c>
       <c r="V5" t="n">
-        <v>1.369</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4307</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8218</v>
+        <v>1.6837</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5654</v>
+        <v>3.3168</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7436</v>
+        <v>-1.6331</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7617</v>
+        <v>1.2261</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8283</v>
+        <v>1.126</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.1001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6138</v>
+        <v>1.5111</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7982</v>
+        <v>1.3994</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8156</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8521</v>
+        <v>-0.2851</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0301</v>
+        <v>-0.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8822</v>
+        <v>-0.0116</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1155</v>
+        <v>0.9535</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>0.2413</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0672</v>
+        <v>0.7123</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>-0.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0187</v>
+        <v>1.0817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8637</v>
+        <v>0.8547</v>
       </c>
       <c r="F7" t="n">
-        <v>0.155</v>
+        <v>0.227</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4998</v>
+        <v>-0.4979</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1053</v>
+        <v>-0.1062</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1776</v>
+        <v>-0.1836</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3222</v>
+        <v>-0.3143</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2547</v>
+        <v>-0.1928</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2032</v>
+        <v>-0.1416</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4909</v>
+        <v>0.7017</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0942</v>
+        <v>0.0243</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.6775</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4211</v>
+        <v>-0.4122</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5784</v>
+        <v>-0.5702</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2808</v>
+        <v>-0.304</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8006</v>
+        <v>-0.8176</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1402</v>
+        <v>-0.1083</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9578</v>
+        <v>0.9755</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8018</v>
+        <v>0.3823</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2521</v>
+        <v>-0.098</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4503</v>
+        <v>0.4802</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7483</v>
+        <v>-1.7432</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5887</v>
+        <v>-1.0517</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.103</v>
+        <v>-0.7752</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4856</v>
+        <v>-0.2766</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1688</v>
+        <v>1.171</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9076</v>
+        <v>0.9103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8609</v>
+        <v>1.8428</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6921</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8335</v>
+        <v>-0.2927</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3648</v>
+        <v>-0.1786</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="10">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.713</v>
+        <v>-2.6785</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9058</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8072</v>
+        <v>-1.7687</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4325</v>
+        <v>-1.4322</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0966</v>
+        <v>-1.0971</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3359</v>
+        <v>-0.3351</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,22 +1234,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1878</v>
+        <v>-0.1568</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0562</v>
+        <v>-2.6838</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1941</v>
+        <v>-2.8298</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1379</v>
+        <v>0.146</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0661</v>
+        <v>-1.0626</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0534</v>
+        <v>0.0545</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.349</v>
+        <v>-0.3419</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0514</v>
+        <v>0.4275</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2087</v>
+        <v>0.1672</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2601</v>
+        <v>0.2603</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5886</v>
+        <v>-5.3083</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.509</v>
+        <v>-5.5129</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0796</v>
+        <v>0.2046</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0546</v>
+        <v>-3.0535</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2078</v>
+        <v>-0.2068</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8468</v>
+        <v>-2.8467</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5647</v>
+        <v>-2.5857</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9147</v>
+        <v>-0.9243</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4898</v>
+        <v>-0.4678</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3919</v>
+        <v>0.6736</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5243</v>
+        <v>0.5571</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1325</v>
+        <v>0.1165</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5914</v>
+        <v>-0.5822000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3794</v>
+        <v>-6.4849</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4303</v>
+        <v>-6.4154</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0509</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.429</v>
+        <v>-3.4363</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2322</v>
+        <v>-2.2371</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1968</v>
+        <v>-1.1992</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8865</v>
+        <v>-2.924</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.356</v>
+        <v>-2.3797</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5425</v>
+        <v>-0.5124</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0015</v>
+        <v>-0.0893</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0998</v>
+        <v>-0.0283</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0983</v>
+        <v>-0.0611</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07010000000000005</v>
+        <v>0.9803000000000006</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0317</v>
+        <v>-0.2982000000000014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9617999999999989</v>
+        <v>1.2784</v>
       </c>
       <c r="G14" t="n">
-        <v>4.022599999999997</v>
+        <v>4.041000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>8.340499999999997</v>
+        <v>8.329600000000005</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.318</v>
+        <v>-4.2888</v>
       </c>
       <c r="J14" t="n">
-        <v>7.732299999999999</v>
+        <v>7.514499999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4666</v>
+        <v>6.326199999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2654</v>
+        <v>1.1882</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7095</v>
+        <v>-3.4739</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8738</v>
+        <v>2.0034</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.583499999999999</v>
+        <v>-5.4771</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1467</v>
+        <v>-18.2104</v>
       </c>
       <c r="R14" t="n">
-        <v>13.61</v>
+        <v>13.6579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6048999999999998</v>
+        <v>1.6499</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4838999999999999</v>
+        <v>0.5775</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0886</v>
+        <v>1.0723</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1606</v>
+        <v>-0.1577000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>9.866300000000001</v>
+        <v>9.8203</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.0272</v>
+        <v>-9.9779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8175</v>
+        <v>3.2677</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0283</v>
+        <v>2.5282</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7892</v>
+        <v>0.7395</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3329</v>
+        <v>2.2294</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1886</v>
+        <v>0.6718</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8557</v>
+        <v>1.5576</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9691</v>
+        <v>2.9025</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.337</v>
+        <v>1.1754</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.7271</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.302</v>
+        <v>-0.6731</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8516</v>
+        <v>-0.5036</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4504</v>
+        <v>-0.1695</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>2.725</v>
+        <v>-0.2788</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1383</v>
+        <v>-0.3256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5867</v>
+        <v>0.0468</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6107</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2819</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3982</v>
+        <v>2.8761</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0936</v>
+        <v>2.1992</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3046</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2365</v>
+        <v>-0.348</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6666</v>
+        <v>-1.2108</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5699</v>
+        <v>0.8628</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9335</v>
+        <v>0.9264</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1878</v>
+        <v>-0.3769</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7458</v>
+        <v>1.3033</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-1.2744</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5212</v>
+        <v>-0.8339</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-0.4405</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>3.1868</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1578</v>
+        <v>0.8035</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7984</v>
+        <v>0.3734</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3593</v>
+        <v>0.4302</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0.5995</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>2.2653</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.6658</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7282</v>
+        <v>2.3951</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9338</v>
+        <v>1.2681</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7945</v>
+        <v>1.127</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5154</v>
+        <v>1.5115</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4732</v>
+        <v>0.4766</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4721</v>
+        <v>1.4519</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3753</v>
+        <v>1.3624</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0433</v>
+        <v>0.0597</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.116</v>
+        <v>-0.4506</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5777</v>
+        <v>-0.2669</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5187</v>
+        <v>2.0585</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6592</v>
+        <v>1.2314</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8596</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6142</v>
+        <v>1.6207</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2308</v>
+        <v>0.2353</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3834</v>
+        <v>1.3854</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8368</v>
+        <v>2.8229</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2225</v>
+        <v>-1.2022</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8099</v>
+        <v>-0.2834</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8166</v>
+        <v>-0.2257</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0066</v>
+        <v>-0.0578</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1929</v>
+        <v>-0.1893</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1929</v>
+        <v>-0.1893</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6841</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4383</v>
+        <v>0.184</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2459</v>
+        <v>0.377</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.325</v>
+        <v>-0.3212</v>
       </c>
       <c r="H19" t="n">
-        <v>0.528</v>
+        <v>0.5339</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.853</v>
+        <v>-0.8551</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3989</v>
+        <v>0.3795</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7029</v>
+        <v>0.6927</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8656</v>
+        <v>0.727</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2662</v>
+        <v>0.0322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5994</v>
+        <v>0.6948</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6711</v>
+        <v>-1.6658</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6711</v>
+        <v>-1.6658</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.256</v>
+        <v>0.3719</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0743</v>
+        <v>0.4152</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1816</v>
+        <v>-0.0433</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2952</v>
+        <v>0.3009</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0188</v>
+        <v>-1.0114</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3141</v>
+        <v>1.3123</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3824</v>
+        <v>0.3715</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0871</v>
+        <v>-0.0706</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0127</v>
+        <v>0.0907</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4561</v>
+        <v>0.2047</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2965</v>
+        <v>-0.1709</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5591</v>
+        <v>-0.5643</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2626</v>
+        <v>0.3934</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3104</v>
+        <v>-0.3103</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4386</v>
+        <v>0.4421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.42</v>
+        <v>-0.4249</v>
       </c>
       <c r="K21" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2129</v>
+        <v>-0.0882</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9883</v>
+        <v>-0.399</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1953</v>
+        <v>0.0278</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.793</v>
+        <v>-0.4268</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6912</v>
+        <v>-0.6881</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2136</v>
+        <v>-1.2094</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5224</v>
+        <v>0.5213</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0251</v>
+        <v>0.0143</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7023</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6581</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3811</v>
+        <v>-0.1443</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.277</v>
+        <v>0.0675</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2371</v>
+        <v>-0.945</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9432</v>
+        <v>-0.4956</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2939</v>
+        <v>-0.4494</v>
       </c>
       <c r="G23" t="n">
-        <v>0.234</v>
+        <v>0.2465</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1632</v>
+        <v>-0.1528</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3972</v>
+        <v>0.3993</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2724</v>
+        <v>1.2631</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6317</v>
+        <v>0.6254</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7906</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1833</v>
+        <v>-0.0066</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3855</v>
+        <v>-1.0032</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5362</v>
+        <v>-2.1184</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1507</v>
+        <v>1.1151</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5516</v>
+        <v>-3.5605</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0878</v>
+        <v>-3.0957</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4638</v>
+        <v>-0.4648</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2145</v>
+        <v>-2.2425</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9852</v>
+        <v>-2.0037</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3371</v>
+        <v>-1.318</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4258</v>
+        <v>-0.0163</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>-0.2047</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2516</v>
+        <v>0.1884</v>
       </c>
       <c r="V24" t="n">
-        <v>3.9529</v>
+        <v>3.9394</v>
       </c>
       <c r="W24" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5439</v>
+        <v>-3.9014</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5295</v>
+        <v>-2.9639</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0144</v>
+        <v>-0.9375</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.1152</v>
+        <v>-4.1287</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.1498</v>
+        <v>-4.1583</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4894</v>
+        <v>-3.5118</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.1108</v>
+        <v>-3.1241</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6258</v>
+        <v>-0.6169</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.039</v>
+        <v>-1.0342</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7566</v>
+        <v>0.4063</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9599</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2032</v>
+        <v>-0.1416</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.8814</v>
+        <v>-4.256</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4258</v>
+        <v>-2.9903</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4556</v>
+        <v>-1.2657</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5915</v>
+        <v>-0.593</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1442</v>
+        <v>0.1491</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7357</v>
+        <v>-0.7421</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4567</v>
+        <v>-0.4791</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1348</v>
+        <v>-0.1139</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7682</v>
+        <v>-0.1394</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6593</v>
+        <v>-0.1862</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1089</v>
+        <v>0.0468</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07000000000000028</v>
+        <v>0.8547999999999991</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.9615999999999998</v>
+        <v>-1.278599999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0318</v>
+        <v>2.1333</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.022500000000001</v>
+        <v>-4.0408</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.340400000000001</v>
+        <v>-8.329599999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>4.318</v>
+        <v>4.2889</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7097</v>
+        <v>3.473800000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8737</v>
+        <v>-2.0032</v>
       </c>
       <c r="L27" t="n">
-        <v>5.583500000000001</v>
+        <v>5.477</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.732000000000001</v>
+        <v>-7.5144</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.466699999999999</v>
+        <v>-6.326300000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.2654</v>
+        <v>-1.1882</v>
       </c>
       <c r="P27" t="n">
-        <v>4.5366</v>
+        <v>4.552599999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R27" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6047999999999998</v>
+        <v>0.1854</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.0886</v>
+        <v>-1.0724</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4838</v>
+        <v>1.2575</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1607000000000001</v>
+        <v>0.1577999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>10.0272</v>
+        <v>9.978</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.866399999999999</v>
+        <v>-9.8203</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104532_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104532_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.7432</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5822000000000001</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.9779</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6658</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.0316</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1893</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6658</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.0316</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104532_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-9.8203</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
